--- a/data/products_docs/product_aircon.xlsx
+++ b/data/products_docs/product_aircon.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29108"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D1564CB-C6B9-4AEF-822F-8775DF8021C8}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maru/Documents/vscode/MemoryPersistence/data/products_docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE5EFEE-C76D-4A40-A1B5-B814EB0E41A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="14800" windowHeight="8020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -52,17 +57,20 @@
   </si>
   <si>
     <t>冷房・暖房機能付き。夏にも冬にも使えます。</t>
+  </si>
+  <si>
+    <t>item001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -70,7 +78,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -100,7 +108,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -433,9 +441,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,9 +457,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2">
-        <v>1</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>

--- a/data/products_docs/product_aircon.xlsx
+++ b/data/products_docs/product_aircon.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29108"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maru/Documents/vscode/MemoryPersistence/data/products_docs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE5EFEE-C76D-4A40-A1B5-B814EB0E41A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_3F8216BDF2DCCE836B02CE998F0AE45F5E522874" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AE8B49A-137B-49C1-9862-099AF205E899}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="14800" windowHeight="8020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>id</t>
   </si>
@@ -50,6 +45,12 @@
     <t>description</t>
   </si>
   <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>item201</t>
+  </si>
+  <si>
     <t>エアコン</t>
   </si>
   <si>
@@ -57,20 +58,17 @@
   </si>
   <si>
     <t>冷房・暖房機能付き。夏にも冬にも使えます。</t>
-  </si>
-  <si>
-    <t>item001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -78,9 +76,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Meiryo UI"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
     </font>
   </fonts>
   <fills count="2">
@@ -103,12 +104,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -440,10 +442,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,19 +461,25 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>
